--- a/zh-TW/snomed-mappings.xlsx
+++ b/zh-TW/snomed-mappings.xlsx
@@ -1,2307 +1,1926 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="生活習慣與危害類別" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOINC-SNOMED 對照(核心資料集)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="生活習慣與危害類別" sheetId="1" r:id="rId1"/>
+    <sheet name="LOINC-SNOMED 對照(核心資料集)" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>類別 Category</t>
+          <t xml:space="preserve">類別 Category</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>SNOMED CT Code</t>
+          <t xml:space="preserve">SNOMED CT Code</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t xml:space="preserve">Display</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>用途/來源 (FSH)</t>
+          <t xml:space="preserve">用途/來源 (FSH)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>生活習慣-嚼檳榔</t>
+          <t xml:space="preserve">生活習慣-嚼檳榔</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>698188003</t>
+          <t xml:space="preserve">698188003</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chews betel quid</t>
+          <t xml:space="preserve">Chews betel quid</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>TWHA-SocialHistory-BetelNut.code (fsh/profiles/TWHA-SocialHistory.fsh)</t>
+          <t xml:space="preserve">TWHA-SocialHistory-BetelNut.code (fsh/profiles/TWHA-SocialHistory.fsh)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>生活習慣-吸菸</t>
+          <t xml:space="preserve">生活習慣-吸菸</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>266919005</t>
+          <t xml:space="preserve">266919005</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Never smoked tobacco</t>
+          <t xml:space="preserve">Never smoked tobacco</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>obs-smoking example (fsh/examples/examples.fsh)</t>
+          <t xml:space="preserve">obs-smoking example (fsh/examples/examples.fsh)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>健康管理分級</t>
+          <t xml:space="preserve">健康管理分級</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>371607000</t>
+          <t xml:space="preserve">371607000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Classification of health status (finding)</t>
+          <t xml:space="preserve">Classification of health status (finding)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TWHA-HealthManagementLevel.code</t>
+          <t xml:space="preserve">TWHA-HealthManagementLevel.code</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>臨場服務-危害發現</t>
+          <t xml:space="preserve">臨場服務-危害發現</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>278486003</t>
+          <t xml:space="preserve">278486003</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Occupational health hazard (finding)</t>
+          <t xml:space="preserve">Occupational health hazard (finding)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TWHA-Observation-ServiceFinding.code</t>
+          <t xml:space="preserve">TWHA-Observation-ServiceFinding.code</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>臨場服務-健康諮詢</t>
+          <t xml:space="preserve">臨場服務-健康諮詢</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>315640000</t>
+          <t xml:space="preserve">315640000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Occupational health counseling (procedure)</t>
+          <t xml:space="preserve">Occupational health counseling (procedure)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TWHA-Task-ServiceTask.code</t>
+          <t xml:space="preserve">TWHA-Task-ServiceTask.code</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>item_name_zh</t>
+          <t xml:space="preserve">item_name_zh</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>item_name_en</t>
+          <t xml:space="preserve">item_name_en</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>loinc_preferred</t>
+          <t xml:space="preserve">loinc_preferred</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>loinc_acceptable</t>
+          <t xml:space="preserve">loinc_acceptable</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>snomed_ct</t>
+          <t xml:space="preserve">snomed_ct</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>snomed_display</t>
+          <t xml:space="preserve">snomed_display</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>snomed_status</t>
+          <t xml:space="preserve">snomed_status</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>ucum_unit</t>
+          <t xml:space="preserve">ucum_unit</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>regulatory_ref</t>
+          <t xml:space="preserve">regulatory_ref</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>血液學</t>
+          <t xml:space="preserve">血液學</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>白血球計數</t>
+          <t xml:space="preserve">白血球計數</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WBC Count</t>
+          <t xml:space="preserve">WBC Count</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6690-2</t>
+          <t xml:space="preserve">6690-2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>{804-5, 26464-8}</t>
+          <t xml:space="preserve">{804-5, 26464-8}</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>767002</t>
+          <t xml:space="preserve">767002</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>White blood cell count (procedure)</t>
+          <t xml:space="preserve">White blood cell count (procedure)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10*3/uL</t>
+          <t xml:space="preserve">10*3/uL</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>附表九 CBC</t>
+          <t xml:space="preserve">附表九 CBC</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>血液學</t>
+          <t xml:space="preserve">血液學</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>血紅素</t>
+          <t xml:space="preserve">血紅素</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hemoglobin</t>
+          <t xml:space="preserve">Hemoglobin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>718-7</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t xml:space="preserve">718-7</t>
+        </is>
+      </c>
+      <c r="E3"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>38082009</t>
+          <t xml:space="preserve">38082009</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hemoglobin (substance)</t>
+          <t xml:space="preserve">Hemoglobin (substance)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>g/dL</t>
+          <t xml:space="preserve">g/dL</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>附表九</t>
+          <t xml:space="preserve">附表九</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>血液學</t>
+          <t xml:space="preserve">血液學</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>血小板</t>
+          <t xml:space="preserve">血小板</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Platelet Count</t>
+          <t xml:space="preserve">Platelet Count</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>777-3</t>
+          <t xml:space="preserve">777-3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>{26515-7}</t>
+          <t xml:space="preserve">{26515-7}</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61928009</t>
+          <t xml:space="preserve">61928009</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platelet count (procedure)</t>
+          <t xml:space="preserve">Platelet count (procedure)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10*3/uL</t>
+          <t xml:space="preserve">10*3/uL</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>附表九</t>
+          <t xml:space="preserve">附表九</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>血液學</t>
+          <t xml:space="preserve">血液學</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>平均紅血球體積 MCV</t>
+          <t xml:space="preserve">平均紅血球體積 MCV</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MCV</t>
+          <t xml:space="preserve">MCV</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>787-2</t>
+          <t xml:space="preserve">787-2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>{30428-7}</t>
+          <t xml:space="preserve">{30428-7}</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>104133003</t>
+          <t xml:space="preserve">104133003</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mean corpuscular volume determination (procedure)</t>
+          <t xml:space="preserve">Mean corpuscular volume determination (procedure)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>fL</t>
+          <t xml:space="preserve">fL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>附表九</t>
+          <t xml:space="preserve">附表九</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>血液學</t>
+          <t xml:space="preserve">血液學</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>平均紅血球血紅素 MCH</t>
+          <t xml:space="preserve">平均紅血球血紅素 MCH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MCH</t>
+          <t xml:space="preserve">MCH</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>785-6</t>
+          <t xml:space="preserve">785-6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>{28539-5}</t>
+          <t xml:space="preserve">{28539-5}</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>85505000</t>
+          <t xml:space="preserve">85505000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mean corpuscular hemoglobin (observable entity)</t>
+          <t xml:space="preserve">Mean corpuscular hemoglobin (observable entity)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>pg</t>
+          <t xml:space="preserve">pg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>附表九</t>
+          <t xml:space="preserve">附表九</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>血液學</t>
+          <t xml:space="preserve">血液學</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>平均紅血球血紅素濃度 MCHC</t>
+          <t xml:space="preserve">平均紅血球血紅素濃度 MCHC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MCHC</t>
+          <t xml:space="preserve">MCHC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>786-4</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t xml:space="preserve">786-4</t>
+        </is>
+      </c>
+      <c r="E7"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>37254006</t>
+          <t xml:space="preserve">37254006</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Mean corpuscular hemoglobin concentration determination (procedure)</t>
+          <t xml:space="preserve">Mean corpuscular hemoglobin concentration determination (procedure)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>g/dL</t>
+          <t xml:space="preserve">g/dL</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>附表九</t>
+          <t xml:space="preserve">附表九</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>血液學</t>
+          <t xml:space="preserve">血液學</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>嗜中性球百分比</t>
+          <t xml:space="preserve">嗜中性球百分比</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Neutrophil %</t>
+          <t xml:space="preserve">Neutrophil %</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>770-8</t>
+          <t xml:space="preserve">770-8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>{26508-2}</t>
+          <t xml:space="preserve">{26508-2}</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>271036002</t>
+          <t xml:space="preserve">271036002</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neutrophil percent differential count (observable entity)</t>
+          <t xml:space="preserve">Neutrophil percent differential count (observable entity)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>%</t>
+          <t xml:space="preserve">%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>附表九</t>
+          <t xml:space="preserve">附表九</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>生化/腎功能</t>
+          <t xml:space="preserve">生化/腎功能</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>空腹血糖</t>
+          <t xml:space="preserve">空腹血糖</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fasting Glucose</t>
+          <t xml:space="preserve">Fasting Glucose</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1558-6</t>
+          <t xml:space="preserve">1558-6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>{2339-0}</t>
+          <t xml:space="preserve">{2339-0}</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>33747003</t>
+          <t xml:space="preserve">33747003</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fasting blood glucose measurement (procedure)</t>
+          <t xml:space="preserve">Fasting blood glucose measurement (procedure)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>mg/dL</t>
+          <t xml:space="preserve">mg/dL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>附表九/成健</t>
+          <t xml:space="preserve">附表九/成健</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>生化/腎功能</t>
+          <t xml:space="preserve">生化/腎功能</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>肌酸酐</t>
+          <t xml:space="preserve">肌酸酐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Creatinine</t>
+          <t xml:space="preserve">Creatinine</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2160-0</t>
+          <t xml:space="preserve">2160-0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>{38483-4}</t>
+          <t xml:space="preserve">{38483-4}</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>15373003</t>
+          <t xml:space="preserve">15373003</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Creatinine measurement (procedure)</t>
+          <t xml:space="preserve">Creatinine measurement (procedure)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>mg/dL</t>
+          <t xml:space="preserve">mg/dL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>附表九</t>
+          <t xml:space="preserve">附表九</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>生化/腎功能</t>
+          <t xml:space="preserve">生化/腎功能</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>腎絲球過濾率 eGFR</t>
+          <t xml:space="preserve">腎絲球過濾率 eGFR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>eGFR (CKD-EPI 2021)</t>
+          <t xml:space="preserve">eGFR (CKD-EPI 2021)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>88293-6</t>
+          <t xml:space="preserve">98979-8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>{33914-3}</t>
+          <t xml:space="preserve">{33914-3}</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>80274001</t>
+          <t xml:space="preserve">80274001</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Glomerular filtration rate (observable entity)</t>
+          <t xml:space="preserve">Glomerular filtration rate (observable entity)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>mL/min/{1.73_m2}</t>
+          <t xml:space="preserve">mL/min/{1.73_m2}</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>成健</t>
+          <t xml:space="preserve">成健</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>生化/腎功能</t>
+          <t xml:space="preserve">生化/腎功能</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>尿酸</t>
+          <t xml:space="preserve">尿酸</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uric Acid</t>
+          <t xml:space="preserve">Uric Acid</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3084-1</t>
+          <t xml:space="preserve">3084-1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>{49154-8}</t>
+          <t xml:space="preserve">(-確定無合適碼)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>86228006</t>
+          <t xml:space="preserve">86228006</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Uric acid measurement (procedure)</t>
+          <t xml:space="preserve">Uric acid measurement (procedure)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>mg/dL</t>
+          <t xml:space="preserve">mg/dL</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>附表九</t>
+          <t xml:space="preserve">附表九</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>肝功能</t>
+          <t xml:space="preserve">肝功能</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>麩草酸轉胺酶 AST</t>
+          <t xml:space="preserve">麩草酸轉胺酶 AST</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AST (GOT)</t>
+          <t xml:space="preserve">AST (GOT)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1920-8</t>
+          <t xml:space="preserve">1920-8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>{14409-7}</t>
+          <t xml:space="preserve">{14409-7}</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>45896001</t>
+          <t xml:space="preserve">45896001</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Aspartate aminotransferase measurement (procedure)</t>
+          <t xml:space="preserve">Aspartate aminotransferase measurement (procedure)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>U/L</t>
+          <t xml:space="preserve">U/L</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>附表九/成健</t>
+          <t xml:space="preserve">附表九/成健</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>肝功能</t>
+          <t xml:space="preserve">肝功能</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>麩丙酮酸轉胺酶 ALT</t>
+          <t xml:space="preserve">麩丙酮酸轉胺酶 ALT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ALT (GPT)</t>
+          <t xml:space="preserve">ALT (GPT)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1742-6</t>
+          <t xml:space="preserve">1742-6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>{14390-9}</t>
+          <t xml:space="preserve">{14390-9}</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>34608000</t>
+          <t xml:space="preserve">34608000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alanine aminotransferase measurement (procedure)</t>
+          <t xml:space="preserve">Alanine aminotransferase measurement (procedure)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>U/L</t>
+          <t xml:space="preserve">U/L</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>附表九/成健</t>
+          <t xml:space="preserve">附表九/成健</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>肝功能</t>
+          <t xml:space="preserve">肝功能</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>鹼性磷酸酶 ALP</t>
+          <t xml:space="preserve">鹼性磷酸酶 ALP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alkaline Phosphatase</t>
+          <t xml:space="preserve">Alkaline Phosphatase</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6768-6</t>
+          <t xml:space="preserve">6768-6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>{1783-0}</t>
+          <t xml:space="preserve">{1783-0}</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>88810008</t>
+          <t xml:space="preserve">88810008</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alkaline phosphatase measurement (procedure)</t>
+          <t xml:space="preserve">Alkaline phosphatase measurement (procedure)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>U/L</t>
+          <t xml:space="preserve">U/L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>附表九</t>
+          <t xml:space="preserve">附表九</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>脂質</t>
+          <t xml:space="preserve">脂質</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>總膽固醇</t>
+          <t xml:space="preserve">總膽固醇</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Total Cholesterol</t>
+          <t xml:space="preserve">Total Cholesterol</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2093-3</t>
+          <t xml:space="preserve">2093-3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>{35200-5}</t>
+          <t xml:space="preserve">{35200-5}</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>77068002</t>
+          <t xml:space="preserve">77068002</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cholesterol measurement (procedure)</t>
+          <t xml:space="preserve">Cholesterol measurement (procedure)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>mg/dL</t>
+          <t xml:space="preserve">mg/dL</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>成健</t>
+          <t xml:space="preserve">成健</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>脂質</t>
+          <t xml:space="preserve">脂質</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>三酸甘油酯</t>
+          <t xml:space="preserve">三酸甘油酯</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Triglycerides</t>
+          <t xml:space="preserve">Triglycerides</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2571-8</t>
+          <t xml:space="preserve">2571-8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>{3043-7}</t>
+          <t xml:space="preserve">{3043-7}</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>14740000</t>
+          <t xml:space="preserve">14740000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Triglyceride measurement (procedure)</t>
+          <t xml:space="preserve">Triglyceride measurement (procedure)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>mg/dL</t>
+          <t xml:space="preserve">mg/dL</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>成健</t>
+          <t xml:space="preserve">成健</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>脂質</t>
+          <t xml:space="preserve">脂質</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>高密度脂蛋白膽固醇 HDL-C</t>
+          <t xml:space="preserve">高密度脂蛋白膽固醇 HDL-C</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HDL Cholesterol</t>
+          <t xml:space="preserve">HDL Cholesterol</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2085-9</t>
+          <t xml:space="preserve">2085-9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>{3048-6}</t>
+          <t xml:space="preserve">{3048-6}</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17888004</t>
+          <t xml:space="preserve">17888004</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>High density lipoprotein measurement (procedure)</t>
+          <t xml:space="preserve">High density lipoprotein measurement (procedure)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>mg/dL</t>
+          <t xml:space="preserve">mg/dL</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>成健</t>
+          <t xml:space="preserve">成健</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>脂質</t>
+          <t xml:space="preserve">脂質</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>低密度脂蛋白膽固醇 LDL-C (計算)</t>
+          <t xml:space="preserve">低密度脂蛋白膽固醇 LDL-C (計算)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LDL Cholesterol (calculated)</t>
+          <t xml:space="preserve">LDL Cholesterol (calculated)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>13457-7</t>
+          <t xml:space="preserve">13457-7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>{18262-6}</t>
+          <t xml:space="preserve">{18262-6}</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>113079009</t>
+          <t xml:space="preserve">113079009</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Low density lipoprotein measurement (procedure)</t>
+          <t xml:space="preserve">Low density lipoprotein measurement (procedure)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>mg/dL</t>
+          <t xml:space="preserve">mg/dL</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>成健</t>
+          <t xml:space="preserve">成健</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>內分泌</t>
+          <t xml:space="preserve">內分泌</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>糖化血色素 HbA1c (NGSP)</t>
+          <t xml:space="preserve">糖化血色素 HbA1c (NGSP)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HbA1c (NGSP %)</t>
+          <t xml:space="preserve">HbA1c (NGSP %)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4548-4</t>
+          <t xml:space="preserve">4548-4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>{59261-8}</t>
+          <t xml:space="preserve">{59261-8}</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>43396009</t>
+          <t xml:space="preserve">43396009</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hemoglobin A1c measurement (procedure)</t>
+          <t xml:space="preserve">Hemoglobin A1c measurement (procedure)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>%</t>
+          <t xml:space="preserve">%</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>成健/進階</t>
+          <t xml:space="preserve">成健/進階</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>內分泌</t>
+          <t xml:space="preserve">內分泌</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>甲狀腺刺激素 TSH</t>
+          <t xml:space="preserve">甲狀腺刺激素 TSH</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thyroid-stimulating hormone</t>
+          <t xml:space="preserve">Thyroid-stimulating hormone</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>11580-8</t>
+          <t xml:space="preserve">11580-8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>{3016-3}</t>
+          <t xml:space="preserve">{3016-3}</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61167004</t>
+          <t xml:space="preserve">61167004</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Measurement of thyroid stimulating hormone (procedure)</t>
+          <t xml:space="preserve">Measurement of thyroid stimulating hormone (procedure)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>mIU/L</t>
+          <t xml:space="preserve">mIU/L</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>進階</t>
+          <t xml:space="preserve">進階</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>癌症標記</t>
+          <t xml:space="preserve">癌症標記</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>前列腺特異性抗原 PSA</t>
+          <t xml:space="preserve">前列腺特異性抗原 PSA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Prostate Specific Antigen</t>
+          <t xml:space="preserve">Prostate Specific Antigen</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2857-1</t>
+          <t xml:space="preserve">2857-1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>{19199-9}</t>
+          <t xml:space="preserve">{19199-9}</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>63476009</t>
+          <t xml:space="preserve">63476009</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Prostate specific antigen measurement (procedure)</t>
+          <t xml:space="preserve">Prostate specific antigen measurement (procedure)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ng/mL</t>
+          <t xml:space="preserve">ng/mL</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>進階</t>
+          <t xml:space="preserve">進階</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>癌症標記</t>
+          <t xml:space="preserve">癌症標記</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>卵巢癌指標 CA-125</t>
+          <t xml:space="preserve">卵巢癌指標 CA-125</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cancer Antigen 125</t>
+          <t xml:space="preserve">Cancer Antigen 125</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10334-1</t>
+          <t xml:space="preserve">10334-1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>{83082-8}</t>
+          <t xml:space="preserve">{83082-8}</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>50610001</t>
+          <t xml:space="preserve">50610001</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cancer antigen 125 measurement (procedure)</t>
+          <t xml:space="preserve">Cancer antigen 125 measurement (procedure)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>U/mL</t>
+          <t xml:space="preserve">U/mL</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>進階</t>
+          <t xml:space="preserve">進階</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>癌症標記</t>
+          <t xml:space="preserve">癌症標記</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>癌胚抗原 CEA</t>
+          <t xml:space="preserve">癌胚抗原 CEA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Carcinoembryonic Antigen</t>
+          <t xml:space="preserve">Carcinoembryonic Antigen</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2039-6</t>
+          <t xml:space="preserve">2039-6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>{83085-1}</t>
+          <t xml:space="preserve">{83085-1}</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60267001</t>
+          <t xml:space="preserve">60267001</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carcinoembryonic antigen measurement (procedure)</t>
+          <t xml:space="preserve">Carcinoembryonic antigen measurement (procedure)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ng/mL</t>
+          <t xml:space="preserve">ng/mL</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>進階</t>
+          <t xml:space="preserve">進階</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>肝炎病毒</t>
+          <t xml:space="preserve">肝炎病毒</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B型肝炎表面抗原 HBsAg</t>
+          <t xml:space="preserve">B型肝炎表面抗原 HBsAg</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hepatitis B Surface Antigen</t>
+          <t xml:space="preserve">Hepatitis B Surface Antigen</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5196-1</t>
+          <t xml:space="preserve">5196-1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>{22326-3}</t>
+          <t xml:space="preserve">{22326-3}</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>39082004</t>
+          <t xml:space="preserve">39082004</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatitis B surface antigen measurement (procedure)</t>
+          <t xml:space="preserve">Hepatitis B surface antigen measurement (procedure)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t xml:space="preserve">VERIFIED</t>
+        </is>
+      </c>
+      <c r="I25"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>成健</t>
+          <t xml:space="preserve">成健</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>肝炎病毒</t>
+          <t xml:space="preserve">肝炎病毒</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>C型肝炎抗體 anti-HCV</t>
+          <t xml:space="preserve">C型肝炎抗體 anti-HCV</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hepatitis C Antibody</t>
+          <t xml:space="preserve">Hepatitis C Antibody</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>13955-0</t>
+          <t xml:space="preserve">13955-0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>{47365-2}</t>
+          <t xml:space="preserve">{47365-2}</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>32218006</t>
+          <t xml:space="preserve">32218006</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatitis C antibody measurement (procedure)</t>
+          <t xml:space="preserve">Hepatitis C antibody measurement (procedure)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t xml:space="preserve">VERIFIED</t>
+        </is>
+      </c>
+      <c r="I26"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>成健</t>
+          <t xml:space="preserve">成健</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>尿液</t>
+          <t xml:space="preserve">尿液</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>尿蛋白 (試紙定性)</t>
+          <t xml:space="preserve">尿蛋白 (試紙定性)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Urine Protein (dipstick)</t>
+          <t xml:space="preserve">Urine Protein (dipstick)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5804-0</t>
+          <t xml:space="preserve">5804-0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>{2888-6}</t>
+          <t xml:space="preserve">{2888-6}</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>167273002</t>
+          <t xml:space="preserve">167273002</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Protein in urine (finding)</t>
+          <t xml:space="preserve">Protein in urine (finding)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t xml:space="preserve">VERIFIED</t>
+        </is>
+      </c>
+      <c r="I27"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>附表九/成健</t>
+          <t xml:space="preserve">附表九/成健</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>生理測量</t>
+          <t xml:space="preserve">生理測量</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>身體質量指數 BMI</t>
+          <t xml:space="preserve">身體質量指數 BMI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Body Mass Index</t>
+          <t xml:space="preserve">Body Mass Index</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>39156-5</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t xml:space="preserve">39156-5</t>
+        </is>
+      </c>
+      <c r="E28"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60621009</t>
+          <t xml:space="preserve">60621009</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Body mass index (observable entity)</t>
+          <t xml:space="preserve">Body mass index (observable entity)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>kg/m2</t>
+          <t xml:space="preserve">kg/m2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>成健</t>
+          <t xml:space="preserve">成健</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>生理測量</t>
+          <t xml:space="preserve">生理測量</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>腰臀比 WHR</t>
+          <t xml:space="preserve">腰臀比 WHR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Waist-to-hip ratio</t>
+          <t xml:space="preserve">Waist-to-hip ratio</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>73708-3</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t xml:space="preserve">73708-3</t>
+        </is>
+      </c>
+      <c r="E29"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>248362002</t>
+          <t xml:space="preserve">248362002</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Waist-hip ratio (observable entity)</t>
+          <t xml:space="preserve">Waist-hip ratio (observable entity)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{ratio}</t>
+          <t xml:space="preserve">{ratio}</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>成健</t>
+          <t xml:space="preserve">成健</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>生理測量</t>
+          <t xml:space="preserve">生理測量</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>血壓 Panel</t>
+          <t xml:space="preserve">血壓 Panel</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Blood Pressure Panel</t>
+          <t xml:space="preserve">Blood Pressure Panel</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>55284-4</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t xml:space="preserve">85354-9</t>
+        </is>
+      </c>
+      <c r="E30"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>75367002</t>
+          <t xml:space="preserve">75367002</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Blood pressure (observable entity)</t>
+          <t xml:space="preserve">Blood pressure (observable entity)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t xml:space="preserve">VERIFIED</t>
+        </is>
+      </c>
+      <c r="I30"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>成健</t>
+          <t xml:space="preserve">成健</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>肺功能</t>
+          <t xml:space="preserve">肺功能</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>用力呼氣肺活量 FVC</t>
+          <t xml:space="preserve">用力呼氣肺活量 FVC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Forced Vital Capacity</t>
+          <t xml:space="preserve">Forced Vital Capacity</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>19876-2</t>
+          <t xml:space="preserve">19876-2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>{19868-9;19870-5}</t>
+          <t xml:space="preserve">{19868-9;19870-5}</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>50834005</t>
+          <t xml:space="preserve">50834005</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Forced vital capacity (observable entity)</t>
+          <t xml:space="preserve">Forced vital capacity (observable entity)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>L</t>
+          <t xml:space="preserve">L</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>職業</t>
+          <t xml:space="preserve">職業</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>肺功能</t>
+          <t xml:space="preserve">肺功能</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>第一秒呼氣量 FEV1</t>
+          <t xml:space="preserve">第一秒呼氣量 FEV1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Forced Expiratory Volume 1s</t>
+          <t xml:space="preserve">Forced Expiratory Volume 1s</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20150-9</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t xml:space="preserve">20150-9</t>
+        </is>
+      </c>
+      <c r="E32"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>59328004</t>
+          <t xml:space="preserve">59328004</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Forced expiratory volume in 1 second (observable entity)</t>
+          <t xml:space="preserve">Forced expiratory volume in 1 second (observable entity)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>L</t>
+          <t xml:space="preserve">L</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>職業</t>
+          <t xml:space="preserve">職業</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>視力</t>
+          <t xml:space="preserve">視力</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>視力檢查 Panel</t>
+          <t xml:space="preserve">視力檢查 Panel</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Vision Test Panel</t>
+          <t xml:space="preserve">Vision Test Panel</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>79880-1</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t xml:space="preserve">79880-1</t>
+        </is>
+      </c>
+      <c r="E33"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>363983007</t>
+          <t xml:space="preserve">363983007</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Visual acuity (observable entity)</t>
+          <t xml:space="preserve">Visual acuity (observable entity)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t xml:space="preserve">VERIFIED</t>
+        </is>
+      </c>
+      <c r="I33"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>職業</t>
+          <t xml:space="preserve">職業</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>聽力</t>
+          <t xml:space="preserve">聽力</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>純音聽力 Panel</t>
+          <t xml:space="preserve">純音聽力 Panel</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pure Tone Audiometry Panel</t>
+          <t xml:space="preserve">Pure Tone Audiometry Panel</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>89015-2</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t xml:space="preserve">89015-2</t>
+        </is>
+      </c>
+      <c r="E34"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>406081008</t>
+          <t xml:space="preserve">406081008</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pure tone audiometry (procedure)</t>
+          <t xml:space="preserve">Pure tone audiometry (procedure)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>dB</t>
+          <t xml:space="preserve">dB</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>職業</t>
+          <t xml:space="preserve">職業</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/zh-TW/snomed-mappings.xlsx
+++ b/zh-TW/snomed-mappings.xlsx
@@ -295,7 +295,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -343,7 +343,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -395,7 +395,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -447,7 +447,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -499,7 +499,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I25"/>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I26"/>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I27"/>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">73708-3</t>
+          <t xml:space="preserve">(-確定無合適碼)</t>
         </is>
       </c>
       <c r="E29"/>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I30"/>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">79880-1</t>
+          <t xml:space="preserve">98497-1</t>
         </is>
       </c>
       <c r="E33"/>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I33"/>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">待覆核</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">

--- a/zh-TW/snomed-mappings.xlsx
+++ b/zh-TW/snomed-mappings.xlsx
@@ -208,7 +208,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">category</t>
+          <t xml:space="preserve">﻿category</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">{14409-7}</t>
+          <t xml:space="preserve">{30239-8;88112-8}</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">{14390-9}</t>
+          <t xml:space="preserve">{1743-4;1744-2}</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">{1783-0}</t>
+          <t xml:space="preserve">(-確定無合適碼)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">{3043-7}</t>
+          <t xml:space="preserve">{3043-7;3048-6}</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">{3048-6}</t>
+          <t xml:space="preserve">(-確定無合適碼)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1141,22 +1141,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">低密度脂蛋白膽固醇 LDL-C (計算)</t>
+          <t xml:space="preserve">低密度脂蛋白膽固醇 LDL-C (方法通用)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">LDL Cholesterol (calculated)</t>
+          <t xml:space="preserve">LDL Cholesterol (method-unspecified)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13457-7</t>
+          <t xml:space="preserve">2089-1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">{18262-6}</t>
+          <t xml:space="preserve">{13457-7;18262-6}</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">{19199-9}</t>
+          <t xml:space="preserve">(-確定無合適碼)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">{22326-3}</t>
+          <t xml:space="preserve">{5195-3;63557-3}</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">{47365-2}</t>
+          <t xml:space="preserve">{16128-1}</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">{2888-6}</t>
+          <t xml:space="preserve">{57735-3}</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1645,30 +1645,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">腰臀比 WHR</t>
+          <t xml:space="preserve">腰圍</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Waist-to-hip ratio</t>
+          <t xml:space="preserve">Waist Circumference</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">(-確定無合適碼)</t>
-        </is>
-      </c>
-      <c r="E29"/>
+          <t xml:space="preserve">8280-0</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{8281-8;56086-2;56114-2;56115-9}</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">248362002</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Waist-hip ratio (observable entity)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">276361009</t>
+        </is>
+      </c>
+      <c r="G29"/>
       <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve">待覆核</t>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">{ratio}</t>
+          <t xml:space="preserve">cm</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">成健</t>
+          <t xml:space="preserve">附表九/成健</t>
         </is>
       </c>
     </row>
@@ -1693,28 +1693,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">血壓 Panel</t>
+          <t xml:space="preserve">腰臀比 WHR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blood Pressure Panel</t>
+          <t xml:space="preserve">Waist-to-hip ratio</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">85354-9</t>
+          <t xml:space="preserve">(-確定無合適碼)</t>
         </is>
       </c>
       <c r="E30"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">75367002</t>
+          <t xml:space="preserve">248362002</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blood pressure (observable entity)</t>
+          <t xml:space="preserve">Waist-hip ratio (observable entity)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1722,7 +1722,11 @@
           <t xml:space="preserve">待覆核</t>
         </is>
       </c>
-      <c r="I30"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{ratio}</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">成健</t>
@@ -1732,37 +1736,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">肺功能</t>
+          <t xml:space="preserve">生理測量</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">用力呼氣肺活量 FVC</t>
+          <t xml:space="preserve">血壓 Panel</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forced Vital Capacity</t>
+          <t xml:space="preserve">Blood Pressure Panel</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">19876-2</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{19868-9;19870-5}</t>
-        </is>
-      </c>
+          <t xml:space="preserve">85354-9</t>
+        </is>
+      </c>
+      <c r="E31"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">50834005</t>
+          <t xml:space="preserve">75367002</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forced vital capacity (observable entity)</t>
+          <t xml:space="preserve">Blood pressure (observable entity)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1770,14 +1770,10 @@
           <t xml:space="preserve">待覆核</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L</t>
-        </is>
-      </c>
+      <c r="I31"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">職業</t>
+          <t xml:space="preserve">成健</t>
         </is>
       </c>
     </row>
@@ -1789,28 +1785,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">第一秒呼氣量 FEV1</t>
+          <t xml:space="preserve">用力呼氣肺活量 FVC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forced Expiratory Volume 1s</t>
+          <t xml:space="preserve">Forced Vital Capacity</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">20150-9</t>
-        </is>
-      </c>
-      <c r="E32"/>
+          <t xml:space="preserve">19868-9</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{19876-2;19870-5}</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">59328004</t>
+          <t xml:space="preserve">50834005</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forced expiratory volume in 1 second (observable entity)</t>
+          <t xml:space="preserve">Forced vital capacity (observable entity)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1832,33 +1832,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">視力</t>
+          <t xml:space="preserve">肺功能</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">視力檢查 Panel</t>
+          <t xml:space="preserve">第一秒呼氣量 FEV1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vision Test Panel</t>
+          <t xml:space="preserve">Forced Expiratory Volume 1s</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">98497-1</t>
+          <t xml:space="preserve">20150-9</t>
         </is>
       </c>
       <c r="E33"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">363983007</t>
+          <t xml:space="preserve">59328004</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual acuity (observable entity)</t>
+          <t xml:space="preserve">Forced expiratory volume in 1 second (observable entity)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1866,7 +1866,11 @@
           <t xml:space="preserve">待覆核</t>
         </is>
       </c>
-      <c r="I33"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">職業</t>
@@ -1876,46 +1880,90 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">聽力</t>
+          <t xml:space="preserve">視力</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">純音聽力 Panel</t>
+          <t xml:space="preserve">視力檢查 Panel</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pure Tone Audiometry Panel</t>
+          <t xml:space="preserve">Vision Test Panel</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">89015-2</t>
+          <t xml:space="preserve">98497-1</t>
         </is>
       </c>
       <c r="E34"/>
       <c r="F34" t="inlineStr">
         <is>
+          <t xml:space="preserve">363983007</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visual acuity (observable entity)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">待覆核</t>
+        </is>
+      </c>
+      <c r="I34"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">職業</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聽力</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">純音聽力 Panel</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pure Tone Audiometry Panel</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89015-2</t>
+        </is>
+      </c>
+      <c r="E35"/>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">406081008</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">Pure tone audiometry (procedure)</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">待覆核</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">待覆核</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">dB</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">職業</t>
         </is>

--- a/zh-TW/snomed-mappings.xlsx
+++ b/zh-TW/snomed-mappings.xlsx
@@ -1052,7 +1052,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">{3043-7;3048-6}</t>
+          <t xml:space="preserve">{3043-7;3048-6;1644-4}</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">{57735-3}</t>
+          <t xml:space="preserve">{57735-3;50561-0;2887-8;20454-5}</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1668,7 +1668,11 @@
           <t xml:space="preserve">276361009</t>
         </is>
       </c>
-      <c r="G29"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waist circumference (observable entity)</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve">待覆核</t>
